--- a/Lab 2 - Asset Inventories and Site Maps/Lab 2 - Asset-Inventory.xlsx
+++ b/Lab 2 - Asset Inventories and Site Maps/Lab 2 - Asset-Inventory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ce13b7071c7f233/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{AD4F1651-D95D-44B4-B059-982EF8EFE2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B38B19D-CB12-484E-B4C8-92013AE4A1D2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B187883-9D2F-4E6C-BB37-1F313976FF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page Overview" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="112">
   <si>
     <t>Asset Inventory: Pages</t>
   </si>
@@ -259,21 +259,12 @@
     <t>dicord image</t>
   </si>
   <si>
-    <t>text</t>
-  </si>
-  <si>
     <t>contact info</t>
   </si>
   <si>
-    <t>message box</t>
-  </si>
-  <si>
     <t>giveaways</t>
   </si>
   <si>
-    <t>golf cash</t>
-  </si>
-  <si>
     <t>Not very visually appealing. decent blocking of assets, but could be resized</t>
   </si>
   <si>
@@ -311,6 +302,66 @@
   </si>
   <si>
     <t>All social media links work correctly</t>
+  </si>
+  <si>
+    <t>(all files have nonsense names)</t>
+  </si>
+  <si>
+    <t>Nav bar</t>
+  </si>
+  <si>
+    <t>intro video</t>
+  </si>
+  <si>
+    <t>Needs to be renamed</t>
+  </si>
+  <si>
+    <t>app store</t>
+  </si>
+  <si>
+    <t>android store</t>
+  </si>
+  <si>
+    <t>header</t>
+  </si>
+  <si>
+    <t>profile picture</t>
+  </si>
+  <si>
+    <t>dicord logo</t>
+  </si>
+  <si>
+    <t>Main nav</t>
+  </si>
+  <si>
+    <t>dicord link</t>
+  </si>
+  <si>
+    <t>input info</t>
+  </si>
+  <si>
+    <t>insert contact info</t>
+  </si>
+  <si>
+    <t>user info</t>
+  </si>
+  <si>
+    <t>oneshot contact info</t>
+  </si>
+  <si>
+    <t>contant info and social media links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text </t>
+  </si>
+  <si>
+    <t>tik tok giveway</t>
+  </si>
+  <si>
+    <t>event info</t>
+  </si>
+  <si>
+    <t>Rules for the giveaway</t>
   </si>
 </sst>
 </file>
@@ -429,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -446,6 +497,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,10 +584,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -921,12 +969,14 @@
       <c r="E4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="8"/>
+      <c r="F4" s="8">
+        <v>2024</v>
+      </c>
       <c r="G4" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>11</v>
@@ -946,12 +996,14 @@
         <v>48</v>
       </c>
       <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="F5" s="11">
+        <v>2024</v>
+      </c>
       <c r="G5" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>12</v>
@@ -973,12 +1025,14 @@
       <c r="E6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8">
+        <v>2024</v>
+      </c>
       <c r="G6" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>13</v>
@@ -1000,12 +1054,14 @@
       <c r="E7" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="8"/>
+      <c r="F7" s="8">
+        <v>2024</v>
+      </c>
       <c r="G7" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1024,12 +1080,14 @@
       <c r="E8" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="11">
+        <v>2024</v>
+      </c>
       <c r="G8" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1048,12 +1106,14 @@
       <c r="E9" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="11">
+        <v>2024</v>
+      </c>
       <c r="G9" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1072,12 +1132,14 @@
       <c r="E10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="8"/>
+      <c r="F10" s="8">
+        <v>2024</v>
+      </c>
       <c r="G10" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1096,12 +1158,14 @@
       <c r="E11" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="8"/>
+      <c r="F11" s="8">
+        <v>2024</v>
+      </c>
       <c r="G11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1120,12 +1184,14 @@
       <c r="E12" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="11">
+        <v>2024</v>
+      </c>
       <c r="G12" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1144,12 +1210,14 @@
       <c r="E13" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="8"/>
+      <c r="F13" s="8">
+        <v>2024</v>
+      </c>
       <c r="G13" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1168,12 +1236,14 @@
       <c r="E14" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="11">
+        <v>2024</v>
+      </c>
       <c r="G14" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1190,12 +1260,14 @@
         <v>50</v>
       </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="11">
+        <v>2024</v>
+      </c>
       <c r="G15" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1212,12 +1284,14 @@
       <c r="E16" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="11"/>
+      <c r="F16" s="11">
+        <v>2024</v>
+      </c>
       <c r="G16" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1251,6 +1325,9 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
       <c r="H2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1282,122 +1359,314 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>62</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="8">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>65</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="8">
+        <v>2</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>66</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>67</v>
       </c>
+      <c r="E7" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F7" s="8">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>69</v>
       </c>
+      <c r="E8" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C9" s="8"/>
+      <c r="D9" s="8" t="s">
         <v>70</v>
       </c>
+      <c r="E9" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F9" s="8">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C10" s="8"/>
+      <c r="D10" s="8" t="s">
         <v>71</v>
       </c>
+      <c r="E10" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C11" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>72</v>
       </c>
+      <c r="E11" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D12" t="s">
+      <c r="C12" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>76</v>
       </c>
+      <c r="E12" s="11">
+        <v>2024</v>
+      </c>
+      <c r="F12" s="11">
+        <v>3</v>
+      </c>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D13" t="s">
+      <c r="C13" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>75</v>
       </c>
+      <c r="E13" s="11">
+        <v>2024</v>
+      </c>
+      <c r="F13" s="11">
+        <v>3</v>
+      </c>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>81</v>
-      </c>
+      <c r="B16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F16" s="8">
+        <v>2</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F17" s="8">
+        <v>2</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
